--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92535054209</v>
+        <v>46157.93107910809</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93107910809</v>
+        <v>46157.93364299703</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93364299703</v>
+        <v>46157.93664841498</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93664841498</v>
+        <v>46158.28190893612</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28190893612</v>
+        <v>46158.29708497174</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29708497174</v>
+        <v>46158.2978540632</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2978540632</v>
+        <v>46158.33352104734</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33352104734</v>
+        <v>46158.37208560612</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.14_Наряд_заказы_СТО/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37208560612</v>
+        <v>46158.37424170368</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
